--- a/daily/2026-04-07.xlsx
+++ b/daily/2026-04-07.xlsx
@@ -9907,10 +9907,10 @@
         <v>13.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8</v>
+        <v>1.806</v>
       </c>
       <c r="K2" t="n">
-        <v>1.943</v>
+        <v>1.926</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
         <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.926</v>
       </c>
       <c r="K4" t="n">
-        <v>1.758</v>
+        <v>1.806</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -10147,10 +10147,10 @@
         <v>12.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.877</v>
+        <v>1.87</v>
       </c>
       <c r="K7" t="n">
-        <v>1.877</v>
+        <v>1.87</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -10243,10 +10243,10 @@
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.758</v>
+        <v>1.935</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -10339,10 +10339,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.769</v>
+        <v>1.893</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>2.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.82</v>
+        <v>1.806</v>
       </c>
       <c r="K12" t="n">
         <v>1.926</v>
@@ -10483,10 +10483,10 @@
         <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1.769</v>
+        <v>1.758</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -10531,10 +10531,10 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.735</v>
+        <v>1.769</v>
       </c>
       <c r="K15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -10627,10 +10627,10 @@
         <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.735</v>
+        <v>1.952</v>
       </c>
       <c r="K17" t="n">
-        <v>2.02</v>
+        <v>1.787</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -10723,10 +10723,10 @@
         <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.769</v>
+        <v>1.758</v>
       </c>
       <c r="K19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -10915,10 +10915,10 @@
         <v>5.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.943</v>
+        <v>1.909</v>
       </c>
       <c r="K23" t="n">
-        <v>1.787</v>
+        <v>1.826</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -11299,10 +11299,10 @@
         <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>1.781</v>
+        <v>1.769</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -11347,10 +11347,10 @@
         <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>1.926</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
-        <v>1.833</v>
+        <v>1.357</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -11395,10 +11395,10 @@
         <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1.847</v>
+        <v>1.8</v>
       </c>
       <c r="K33" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
         <v>0.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.943</v>
+        <v>2.75</v>
       </c>
       <c r="K34" t="n">
-        <v>1.82</v>
+        <v>1.417</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -11491,10 +11491,10 @@
         <v>3.7</v>
       </c>
       <c r="J35" t="n">
-        <v>1.952</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1.8</v>
+        <v>1.769</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -11539,10 +11539,10 @@
         <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="K36" t="n">
-        <v>1.741</v>
+        <v>1.385</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -11587,10 +11587,10 @@
         <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="K37" t="n">
-        <v>1.893</v>
+        <v>1.408</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -11635,10 +11635,10 @@
         <v>2.4</v>
       </c>
       <c r="J38" t="n">
-        <v>1.909</v>
+        <v>2.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1.847</v>
+        <v>1.417</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -11683,10 +11683,10 @@
         <v>1.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1.833</v>
+        <v>2.7</v>
       </c>
       <c r="K39" t="n">
-        <v>1.926</v>
+        <v>1.435</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -11731,10 +11731,10 @@
         <v>3.3</v>
       </c>
       <c r="J40" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -11779,10 +11779,10 @@
         <v>1.9</v>
       </c>
       <c r="J41" t="n">
-        <v>1.909</v>
+        <v>2.7</v>
       </c>
       <c r="K41" t="n">
-        <v>1.847</v>
+        <v>1.435</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -11827,10 +11827,10 @@
         <v>1.1</v>
       </c>
       <c r="J42" t="n">
-        <v>1.847</v>
+        <v>1.833</v>
       </c>
       <c r="K42" t="n">
-        <v>1.909</v>
+        <v>1.926</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -11875,10 +11875,10 @@
         <v>0.4</v>
       </c>
       <c r="J43" t="n">
-        <v>1.833</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
-        <v>1.926</v>
+        <v>1.357</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -11923,10 +11923,10 @@
         <v>2.8</v>
       </c>
       <c r="J44" t="n">
-        <v>1.952</v>
+        <v>3.05</v>
       </c>
       <c r="K44" t="n">
-        <v>1.813</v>
+        <v>1.357</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
         <v>6.8</v>
       </c>
       <c r="J59" t="n">
-        <v>1.877</v>
+        <v>2.8</v>
       </c>
       <c r="K59" t="n">
-        <v>1.855</v>
+        <v>1.408</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -12691,10 +12691,10 @@
         <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>1.855</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -12739,10 +12739,10 @@
         <v>9</v>
       </c>
       <c r="J61" t="n">
-        <v>1.847</v>
+        <v>3.1</v>
       </c>
       <c r="K61" t="n">
-        <v>1.885</v>
+        <v>1.345</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -12931,10 +12931,10 @@
         <v>2.7</v>
       </c>
       <c r="J65" t="n">
-        <v>1.885</v>
+        <v>2.75</v>
       </c>
       <c r="K65" t="n">
-        <v>1.847</v>
+        <v>1.417</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -13027,10 +13027,10 @@
         <v>7.1</v>
       </c>
       <c r="J67" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="K67" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>1.926</v>
       </c>
       <c r="K68" t="n">
-        <v>1.82</v>
+        <v>1.806</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>0.2</v>
       </c>
       <c r="J74" t="n">
-        <v>1.909</v>
+        <v>1.893</v>
       </c>
       <c r="K74" t="n">
         <v>1.833</v>
@@ -13507,10 +13507,10 @@
         <v>8.4</v>
       </c>
       <c r="J77" t="n">
-        <v>1.917</v>
+        <v>1.952</v>
       </c>
       <c r="K77" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -13699,10 +13699,10 @@
         <v>2.4</v>
       </c>
       <c r="J81" t="n">
-        <v>1.877</v>
+        <v>2.8</v>
       </c>
       <c r="K81" t="n">
-        <v>1.893</v>
+        <v>1.408</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -14179,10 +14179,10 @@
         <v>8</v>
       </c>
       <c r="J91" t="n">
-        <v>1.787</v>
+        <v>3.1</v>
       </c>
       <c r="K91" t="n">
-        <v>1.98</v>
+        <v>1.345</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -14227,10 +14227,10 @@
         <v>1.8</v>
       </c>
       <c r="J92" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="K92" t="n">
-        <v>1.73</v>
+        <v>1.752</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -14275,10 +14275,10 @@
         <v>3.2</v>
       </c>
       <c r="J93" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K93" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -14323,10 +14323,10 @@
         <v>5</v>
       </c>
       <c r="J94" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K94" t="n">
-        <v>1.84</v>
+        <v>1.385</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -14371,10 +14371,10 @@
         <v>0.9</v>
       </c>
       <c r="J95" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="K95" t="n">
-        <v>1.741</v>
+        <v>1.73</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -14419,10 +14419,10 @@
         <v>4.1</v>
       </c>
       <c r="J96" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="K96" t="n">
-        <v>1.917</v>
+        <v>1.408</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
@@ -14467,10 +14467,10 @@
         <v>2.9</v>
       </c>
       <c r="J97" t="n">
-        <v>1.901</v>
+        <v>1.917</v>
       </c>
       <c r="K97" t="n">
-        <v>1.862</v>
+        <v>1.84</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -14515,10 +14515,10 @@
         <v>2.5</v>
       </c>
       <c r="J98" t="n">
-        <v>1.952</v>
+        <v>2.8</v>
       </c>
       <c r="K98" t="n">
-        <v>1.813</v>
+        <v>1.408</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -14563,10 +14563,10 @@
         <v>9.5</v>
       </c>
       <c r="J99" t="n">
-        <v>1.901</v>
+        <v>3</v>
       </c>
       <c r="K99" t="n">
-        <v>1.862</v>
+        <v>1.364</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
@@ -14611,10 +14611,10 @@
         <v>1.1</v>
       </c>
       <c r="J100" t="n">
-        <v>1.833</v>
+        <v>1.8</v>
       </c>
       <c r="K100" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -14659,10 +14659,10 @@
         <v>1.2</v>
       </c>
       <c r="J101" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K101" t="n">
-        <v>1.877</v>
+        <v>1.357</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -14707,10 +14707,10 @@
         <v>6.6</v>
       </c>
       <c r="J102" t="n">
-        <v>1.787</v>
+        <v>1.813</v>
       </c>
       <c r="K102" t="n">
-        <v>1.98</v>
+        <v>1.962</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -14755,10 +14755,10 @@
         <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="K103" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -14803,10 +14803,10 @@
         <v>5.2</v>
       </c>
       <c r="J104" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="K104" t="n">
-        <v>1.901</v>
+        <v>1.357</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
@@ -14899,10 +14899,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1.99</v>
+        <v>3.05</v>
       </c>
       <c r="K106" t="n">
-        <v>1.794</v>
+        <v>1.357</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
@@ -14947,10 +14947,10 @@
         <v>3.8</v>
       </c>
       <c r="J107" t="n">
-        <v>1.926</v>
+        <v>2.75</v>
       </c>
       <c r="K107" t="n">
-        <v>1.847</v>
+        <v>1.417</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
@@ -14995,10 +14995,10 @@
         <v>1.3</v>
       </c>
       <c r="J108" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="K108" t="n">
-        <v>1.952</v>
+        <v>1.385</v>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
@@ -15043,10 +15043,10 @@
         <v>4.8</v>
       </c>
       <c r="J109" t="n">
-        <v>1.847</v>
+        <v>3.05</v>
       </c>
       <c r="K109" t="n">
-        <v>1.926</v>
+        <v>1.357</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
@@ -15091,10 +15091,10 @@
         <v>2.8</v>
       </c>
       <c r="J110" t="n">
-        <v>1.901</v>
+        <v>2.9</v>
       </c>
       <c r="K110" t="n">
-        <v>1.87</v>
+        <v>1.385</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
@@ -15187,10 +15187,10 @@
         <v>3.6</v>
       </c>
       <c r="J112" t="n">
-        <v>1.926</v>
+        <v>2.65</v>
       </c>
       <c r="K112" t="n">
-        <v>1.847</v>
+        <v>1.455</v>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
@@ -15235,10 +15235,10 @@
         <v>0.3</v>
       </c>
       <c r="J113" t="n">
-        <v>1.862</v>
+        <v>2.6</v>
       </c>
       <c r="K113" t="n">
-        <v>1.909</v>
+        <v>1.465</v>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
@@ -15283,10 +15283,10 @@
         <v>0.7</v>
       </c>
       <c r="J114" t="n">
-        <v>1.962</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>1.813</v>
+        <v>1.364</v>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
@@ -15331,10 +15331,10 @@
         <v>0.7</v>
       </c>
       <c r="J115" t="n">
-        <v>1.917</v>
+        <v>2.65</v>
       </c>
       <c r="K115" t="n">
-        <v>1.855</v>
+        <v>1.455</v>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>

--- a/daily/2026-04-07.xlsx
+++ b/daily/2026-04-07.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -628,7 +646,6 @@
       <c r="V2" t="n">
         <v>11</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>-18.2</v>
       </c>
@@ -952,7 +969,6 @@
       <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>0</v>
       </c>
@@ -1194,7 +1210,6 @@
       <c r="V9" t="n">
         <v>11</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>3.6</v>
       </c>
@@ -1436,7 +1451,6 @@
       <c r="V12" t="n">
         <v>12</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>-7.7</v>
       </c>
@@ -1678,7 +1692,6 @@
       <c r="V15" t="n">
         <v>16</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>0</v>
       </c>
@@ -2084,7 +2097,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-14.3</v>
       </c>
@@ -2326,7 +2338,6 @@
       <c r="V23" t="n">
         <v>14</v>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>9.4</v>
       </c>
@@ -2650,7 +2661,6 @@
       <c r="V27" t="n">
         <v>14</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>-44.7</v>
       </c>
@@ -2728,7 +2738,6 @@
       <c r="V28" t="n">
         <v>14</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>12.5</v>
       </c>
@@ -2888,7 +2897,6 @@
       <c r="V30" t="n">
         <v>30</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>26.6</v>
       </c>
@@ -2966,7 +2974,6 @@
       <c r="V31" t="n">
         <v>14</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>19.2</v>
       </c>
@@ -3044,7 +3051,6 @@
       <c r="V32" t="n">
         <v>4</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
         <v>0.3</v>
       </c>
@@ -3286,7 +3292,6 @@
       <c r="V35" t="n">
         <v>25</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>2.5</v>
       </c>
@@ -4184,7 +4189,6 @@
       <c r="V46" t="n">
         <v>24</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-8.300000000000001</v>
       </c>
@@ -4918,7 +4922,6 @@
       <c r="V55" t="n">
         <v>22</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>-6.7</v>
       </c>
@@ -5242,7 +5245,6 @@
       <c r="V59" t="n">
         <v>24</v>
       </c>
-      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>-13.4</v>
       </c>
@@ -5402,7 +5404,6 @@
       <c r="V61" t="n">
         <v>8</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>0.7</v>
       </c>
@@ -5644,7 +5645,6 @@
       <c r="V64" t="n">
         <v>8</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-1.6</v>
       </c>
@@ -5722,7 +5722,6 @@
       <c r="V65" t="n">
         <v>8</v>
       </c>
-      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>6.1</v>
       </c>
@@ -5800,7 +5799,6 @@
       <c r="V66" t="n">
         <v>8</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>17.8</v>
       </c>
@@ -5960,7 +5958,6 @@
       <c r="V68" t="n">
         <v>8</v>
       </c>
-      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>10.1</v>
       </c>
@@ -6284,7 +6281,6 @@
       <c r="V72" t="n">
         <v>13</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>14.6</v>
       </c>
@@ -6526,7 +6522,6 @@
       <c r="V75" t="n">
         <v>15</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>32.4</v>
       </c>
@@ -6604,7 +6599,6 @@
       <c r="V76" t="n">
         <v>13</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>7.5</v>
       </c>
@@ -6928,7 +6922,6 @@
       <c r="V80" t="n">
         <v>2</v>
       </c>
-      <c r="W80" t="inlineStr"/>
       <c r="X80" t="n">
         <v>4.2</v>
       </c>
@@ -8892,7 +8885,6 @@
       <c r="V104" t="n">
         <v>18</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
         <v>0</v>
       </c>
@@ -9462,7 +9454,6 @@
       <c r="V111" t="n">
         <v>20</v>
       </c>
-      <c r="W111" t="inlineStr"/>
       <c r="X111" t="n">
         <v>-1.1</v>
       </c>
@@ -15543,2303 +15534,5197 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Leonard Miller</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 13 pts vs 17.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 25 played vs L10 avg 24.0. Shooting efficiency was cold: 45.5% FG (-7.6% vs L10 avg of 53.1%). 5/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 3.3 pts — actual 13 was 9.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Miller's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Collin Sexton</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Sexton scored 15 pts vs 22.5 line (-7.5), UNDER hit by 7.5 pts. Sexton played 30 min (+4.8 vs L10 avg of 25.5) — 19% more than expected. Shooting efficiency was cold: 31.2% FG (-16.5% vs L10 avg of 47.7%). 5/16 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 14.1 pts — actual 15 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Sexton in this role.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Guerschon Yabusele</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Yabusele scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Yabusele played 27 min (+3.2 vs L10 avg of 23.7) — 14% more than expected. Shooting efficiency was cold: 33.3% FG (-10.8% vs L10 avg of 44.1%). 3/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 12.7 pts — actual 9 was 3.7 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Yabusele's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Anthony Gill</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gill scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Gill played 16 min (-13.2 vs L10 avg of 28.7) — 46% less than expected. Shooting efficiency was hot: 75.0% FG (+10.8% vs L10 avg of 64.2%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.0 pts — actual 8 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Gill in this role.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 2 pts vs 22.5 line (-20.5), UNDER hit by 20.5 pts. Minutes were as expected: 31 played vs L10 avg 31.4. Shooting efficiency was cold: 7.7% FG (-43.3% vs L10 avg of 51.0%). 1/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 9.4 pts — actual 2 was 7.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Okoro scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Okoro played 16 min (-12.8 vs L10 avg of 29.1) — 44% less than expected. Shooting efficiency was hot: 57.1% FG (+11.0% vs L10 avg of 46.1%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 8.5 pts — actual 11 was 2.5 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Okoro's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Rob Dillingham</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dillingham scored 26 pts vs 11.5 line (+14.5), UNDER missed by 14.5 pts. Dillingham played 27 min (+6.6 vs L10 avg of 20.5) — 32% more than expected. Shooting efficiency was hot: 60.0% FG (+14.3% vs L10 avg of 45.7%). 9/15 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.5 pts — actual 26 was 20.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jones scored 20 pts vs 18.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 27 played vs L10 avg 27.5. Shooting was in line with averages: 53.3% FG (8/15, L10 avg 57.9%). Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.5 pts — actual 20 was 5.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Coulibaly scored 19 pts vs 13.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 24 played vs L10 avg 26.3. Shooting efficiency was hot: 70.0% FG (+25.5% vs L10 avg of 44.5%). 7/10 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.2 pts — actual 19 was 13.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Obi Toppin</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Toppin scored 14 pts vs 11.5 line (+2.5), OVER hit by 2.5 pts. Toppin played 22 min (+3.9 vs L10 avg of 18.2) — 21% more than expected. Shooting efficiency was cold: 30.8% FG (-26.0% vs L10 avg of 56.8%). 4/13 from the field. Signals that called it correctly: Trend, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.1 pts — actual 14 was 5.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Toppin's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Bones Hyland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hyland scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Hyland played 21 min (-5.5 vs L10 avg of 26.2) — 21% less than expected. Shooting efficiency was hot: 55.6% FG (+12.9% vs L10 avg of 42.7%). 5/9 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 6.5 pts — actual 19 was 12.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Hyland for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Mike Conley</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Conley scored 8 pts vs 6.5 line (+1.5), UNDER missed by 1.5 pts. Conley played 21 min (+4.1 vs L10 avg of 16.6) — 25% more than expected. Shooting efficiency was hot: 50.0% FG (+34.7% vs L10 avg of 15.3%). 3/6 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 3.3 pts — actual 8 was 4.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Randle scored 19 pts vs 24.5 line (-5.5), UNDER hit by 5.5 pts. Randle played 28 min (-5.6 vs L10 avg of 33.4) — 17% less than expected. Shooting efficiency was cold: 38.5% FG (-9.9% vs L10 avg of 48.4%). 5/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 18.3 pts — actual 19 was 0.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Randle in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 2 pts vs 10.5 line (-8.5), UNDER hit by 8.5 pts. Brown played 16 min (-8.9 vs L10 avg of 25.4) — 35% less than expected. Shooting efficiency was cold: 50.0% FG (-7.1% vs L10 avg of 57.1%). 1/2 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 6.3 pts — actual 2 was 4.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Brown's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gobert scored 5 pts vs 12.5 line (-7.5), UNDER hit by 7.5 pts. Minutes were as expected: 33 played vs L10 avg 30.5. Shooting efficiency was cold: 40.0% FG (-19.6% vs L10 avg of 59.6%). 2/5 from the field. Signals that called it correctly: Volume, HR L30, Trend, Context, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Defense, Pace. Projection model targeted 9.5 pts — actual 5 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Gobert's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Jarace Walker</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Walker scored 11 pts vs 16.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 28 played vs L10 avg 30.0. Shooting efficiency was cold: 33.3% FG (-17.5% vs L10 avg of 50.8%). 4/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 9.4 pts — actual 11 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN — DiVincenzo scored 11 pts vs 12.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 31 played vs L10 avg 30.5. Shooting was in line with averages: 33.3% FG (4/12, L10 avg 30.6%). Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 11.8 pts — actual 11 was 0.8 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for DiVincenzo in this role.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Jackson played 25 min (+6.9 vs L10 avg of 18.0) — 38% more than expected. Shooting efficiency was cold: 28.6% FG (-21.9% vs L10 avg of 50.5%). 2/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, FG Trend. Projection model targeted 7.4 pts — actual 9 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Micah Potter</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Potter scored 11 pts vs 9.5 line (+1.5), UNDER missed by 1.5 pts. Potter played 22 min (+6.1 vs L10 avg of 16.2) — 38% more than expected. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 64.2%). Counter-signals that proved correct: Volume, Trend, Context, H2H. Signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 7.4 pts — actual 11 was 3.6 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Reid scored 17 pts vs 15.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 24 played vs L10 avg 26.3. Shooting efficiency was hot: 70.0% FG (+34.2% vs L10 avg of 35.8%). 7/10 from the field. Signals that called it correctly: Defense, H2H, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.0 pts — actual 17 was 1.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Reid in this role.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>MIN @ IND</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dosunmu scored 24 pts vs 18.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 33 played vs L10 avg 33.1. Shooting efficiency was hot: 58.8% FG (+6.4% vs L10 avg of 52.4%). 10/17 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.3 pts — actual 24 was 5.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Josh Minott</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>AJ Green</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 20 pts vs 14.5 line (+5.5), UNDER missed by 5.5 pts. Green played 39 min (+11.6 vs L10 avg of 27.0) — 43% more than expected. Shooting efficiency was hot: 46.2% FG (+5.6% vs L10 avg of 40.6%). 6/13 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.0 pts — actual 20 was 11.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Jericho Sims</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sims scored 12 pts vs 8.5 line (+3.5), UNDER missed by 3.5 pts. Sims played 36 min (+12.2 vs L10 avg of 24.3) — 50% more than expected. Shooting was in line with averages: 66.7% FG (6/9, L10 avg 68.7%). Counter-signals that proved correct: Trend, Defense. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.5 pts — actual 12 was 5.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Taurean Prince</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Prince scored 16 pts vs 12.5 line (+3.5), UNDER missed by 3.5 pts. Prince played 37 min (+12.2 vs L10 avg of 24.6) — 50% more than expected. Shooting efficiency was cold: 40.0% FG (-6.4% vs L10 avg of 46.4%). 6/15 from the field. Counter-signals that proved correct: Trend, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 3.4 pts — actual 16 was 12.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Traore scored 5 pts vs 14.5 line (-9.5), UNDER hit by 9.5 pts. Traore played 9 min (-15.2 vs L10 avg of 24.5) — 62% less than expected. Shooting efficiency was hot: 100.0% FG (+67.3% vs L10 avg of 32.7%). 2/2 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted -0.3 pts — actual 5 was 5.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Traore's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Ben Saraf</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Saraf scored 19 pts vs 9.5 line (+9.5), OVER hit by 9.5 pts. Saraf played 36 min (+10.3 vs L10 avg of 25.3) — 41% more than expected. Shooting was in line with averages: 38.5% FG (5/13, L10 avg 37.9%). Signals that called it correctly: HR L10, Trend, Defense, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.6 pts — actual 19 was 8.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Saraf's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Jalen Wilson</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Wilson scored 7 pts vs 13.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 19 played vs L10 avg 19.0. Shooting efficiency was cold: 28.6% FG (-17.8% vs L10 avg of 46.4%). 2/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 5.3 pts — actual 7 was 1.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Wilson in this role.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dieng scored 10 pts vs 19.5 line (-9.5), UNDER hit by 9.5 pts. Minutes were as expected: 32 played vs L10 avg 30.4. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 42.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 18.6 pts — actual 10 was 8.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dieng's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>MIL @ BKN</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Powell scored 11 pts vs 9.5 line (+1.5), UNDER missed by 1.5 pts. Powell played 40 min (+14.7 vs L10 avg of 25.8) — 57% more than expected. Shooting efficiency was cold: 25.0% FG (-15.3% vs L10 avg of 40.3%). 4/16 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.1 pts — actual 11 was 4.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ingram scored 23 pts vs 21.5 line (+1.5), UNDER missed by 1.5 pts. Ingram played 29 min (-3.4 vs L10 avg of 32.7) — 10% less than expected. Shooting was in line with averages: 56.2% FG (9/16, L10 avg 51.7%). Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.5 pts — actual 23 was 4.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 25 pts vs 17.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 30 played vs L10 avg 30.5. Shooting efficiency was hot: 62.5% FG (+8.2% vs L10 avg of 54.3%). 10/16 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.2 pts — actual 25 was 8.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 8 pts vs 11.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 26 played vs L10 avg 26.1. Shooting efficiency was cold: 33.3% FG (-15.5% vs L10 avg of 48.8%). 4/12 from the field. Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.2 pts — actual 8 was 6.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Larsson scored 7 pts vs 10.5 line (-3.5), OVER missed by 3.5 pts. Larsson played 26 min (-4.7 vs L10 avg of 30.9) — 15% less than expected. Shooting efficiency was cold: 22.2% FG (-29.9% vs L10 avg of 52.1%). 2/9 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.5 pts — actual 7 was 5.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Larsson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Poeltl scored 17 pts vs 11.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 26 played vs L10 avg 24.4. Shooting was in line with averages: 61.5% FG (8/13, L10 avg 63.6%). Signals that called it correctly: HR L10, Trend, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 12.3 pts — actual 17 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Poeltl's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Norman Powell</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 14 pts vs 17.5 line (-3.5), UNDER hit by 3.5 pts. Powell played 24 min (-3.8 vs L10 avg of 27.6) — 14% less than expected. Shooting efficiency was cold: 33.3% FG (-12.0% vs L10 avg of 45.3%). 4/12 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.6 pts — actual 14 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Powell in this role.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Wiggins scored 24 pts vs 13.5 line (+10.5), OVER hit by 10.5 pts. Wiggins played 33 min (+5.1 vs L10 avg of 27.6) — 18% more than expected. Shooting efficiency was hot: 61.5% FG (+10.4% vs L10 avg of 51.1%). 8/13 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.9 pts — actual 24 was 10.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wiggins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mamukelashvili scored 11 pts vs 9.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 22 played vs L10 avg 22.2. Shooting efficiency was cold: 44.4% FG (-14.2% vs L10 avg of 58.6%). 4/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (10/10 aligned). Projection model targeted 12.3 pts — actual 11 was 1.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (10/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Adebayo scored 7 pts vs 21.5 line (-14.5), UNDER hit by 14.5 pts. Minutes were as expected: 36 played vs L10 avg 35.1. Shooting efficiency was cold: 15.4% FG (-25.3% vs L10 avg of 40.7%). 2/13 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, Context, Min Trend. Projection model targeted 18.9 pts — actual 7 was 11.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Adebayo's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 9 pts vs 8.5 line (+0.5), OVER hit by 0.5 pts. Mitchell played 23 min (-7.1 vs L10 avg of 30.4) — 23% less than expected. Shooting efficiency was cold: 36.4% FG (-10.8% vs L10 avg of 47.2%). 4/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 10.5 pts — actual 9 was 1.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mitchell in this role.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Immanuel Quickley</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Quickley scored 3 pts vs 13.5 line (-10.5), OVER missed by 10.5 pts. Quickley played 18 min (-14.3 vs L10 avg of 31.9) — 45% less than expected. Shooting efficiency was cold: 33.3% FG (-6.2% vs L10 avg of 39.5%). 1/3 from the field. Counter-signals that proved correct: HR L10, Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.9 pts — actual 3 was 12.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Quickley for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Herro scored 14 pts vs 21.5 line (-7.5), OVER missed by 7.5 pts. Herro played 30 min (-4.0 vs L10 avg of 34.0) — 12% less than expected. Shooting efficiency was hot: 62.5% FG (+18.6% vs L10 avg of 43.9%). 5/8 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 23.8 pts — actual 14 was 9.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Walter scored 9 pts vs 8.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 27.3. Shooting efficiency was cold: 37.5% FG (-17.3% vs L10 avg of 54.8%). 3/8 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context, H2H. Projection model targeted 7.4 pts — actual 9 was 1.6 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barrett scored 16 pts vs 21.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 31 played vs L10 avg 30.3. Shooting efficiency was cold: 43.8% FG (-5.6% vs L10 avg of 49.4%). 7/16 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 24.3 pts — actual 16 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 13 pts vs 17.5 line (-4.5), UNDER hit by 4.5 pts. Knueppel played 35 min (+6.3 vs L10 avg of 29.1) — 22% more than expected. Shooting efficiency was cold: 31.2% FG (-10.3% vs L10 avg of 41.5%). 5/16 from the field. Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.2 pts — actual 13 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Knueppel in this role.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — White scored 12 pts vs 14.5 line (-2.5), OVER missed by 2.5 pts. White played 37 min (+3.0 vs L10 avg of 33.6) — 9% more than expected. Shooting efficiency was hot: 80.0% FG (+35.8% vs L10 avg of 44.2%). 4/5 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 16.8 pts — actual 12 was 4.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Queta scored 12 pts vs 9.5 line (+2.5), UNDER missed by 2.5 pts. Queta played 25 min (-3.5 vs L10 avg of 28.8) — 12% less than expected. Shooting efficiency was hot: 85.7% FG (+14.3% vs L10 avg of 71.4%). 6/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 9.2 pts — actual 12 was 2.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Nikola Vučević</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Vučević scored 2 pts vs 8.5 line (-6.5), OVER missed by 6.5 pts. Vučević played 23 min (+3.2 vs L10 avg of 19.5) — 16% more than expected. Shooting efficiency was cold: 10.0% FG (-27.7% vs L10 avg of 37.7%). 1/10 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.1 pts — actual 2 was 10.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Tatum scored 23 pts vs 22.5 line (+0.5), UNDER missed by 0.5 pts. Tatum played 39 min (+5.9 vs L10 avg of 33.0) — 18% more than expected. Shooting efficiency was hot: 53.3% FG (+11.8% vs L10 avg of 41.5%). 8/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 22.2 pts — actual 23 was 0.8 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Diabaté scored 2 pts vs 7.5 line (-5.5), UNDER hit by 5.5 pts. Diabaté played 33 min (+6.1 vs L10 avg of 26.8) — 23% more than expected. Shooting efficiency was cold: 33.3% FG (-38.5% vs L10 avg of 71.8%). 1/3 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.7 pts — actual 2 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Diabaté's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 13 pts vs 14.5 line (-1.5), UNDER hit by 1.5 pts. Bridges played 32 min (+4.2 vs L10 avg of 27.5) — 15% more than expected. Shooting was in line with averages: 55.6% FG (5/9, L10 avg 57.0%). Signals that called it correctly: HR L30, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 8.2 pts — actual 13 was 4.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Bridges's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Ball scored 36 pts vs 20.5 line (+15.5), OVER hit by 15.5 pts. Ball played 36 min (+8.0 vs L10 avg of 28.5) — 28% more than expected. Shooting efficiency was hot: 50.0% FG (+6.3% vs L10 avg of 43.7%). 12/24 from the field. Signals that called it correctly: Volume, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 26.2 pts — actual 36 was 9.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ball's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 35 pts vs 26.5 line (+8.5), UNDER missed by 8.5 pts. Brown played 43 min (+7.2 vs L10 avg of 36.0) — 20% more than expected. Shooting was in line with averages: 44.8% FG (13/29, L10 avg 46.8%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, Pace. Projection model targeted 24.9 pts — actual 35 was 10.1 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when BOS is involved.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Miller scored 20 pts vs 18.5 line (+1.5), UNDER missed by 1.5 pts. Miller played 34 min (+3.2 vs L10 avg of 30.7) — 10% more than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 47.8%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 15.0 pts — actual 20 was 5.0 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hauser scored 5 pts vs 7.5 line (-2.5), OVER missed by 2.5 pts. Hauser played 16 min (-9.3 vs L10 avg of 25.5) — 36% less than expected. Shooting efficiency was cold: 28.6% FG (-16.1% vs L10 avg of 44.7%). 2/7 from the field. Counter-signals that proved correct: HR L10, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 9.7 pts — actual 5 was 4.7 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Hauser for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Pritchard scored 12 pts vs 14.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 30.8. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 49.8%). Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.3 pts — actual 12 was 8.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Pritchard's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>CHA @ BOS</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 9 pts vs 6.5 line (+2.5), UNDER missed by 2.5 pts. Williams played 26 min (+6.3 vs L10 avg of 19.4) — 32% more than expected. Shooting was in line with averages: 37.5% FG (3/8, L10 avg 42.3%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, Pace. Projection model targeted 4.7 pts — actual 9 was 4.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Williams's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 19 pts vs 16.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 34 played vs L10 avg 33.2. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 43.5%). Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 6.7 pts — actual 19 was 12.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Williams's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Jeremiah Fears</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Fears scored 40 pts vs 19.5 line (+20.5), UNDER missed by 20.5 pts. Fears played 38 min (+12.1 vs L10 avg of 25.7) — 47% more than expected. Shooting efficiency was hot: 58.6% FG (+12.2% vs L10 avg of 46.4%). 17/29 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.3 pts — actual 40 was 25.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Sensabaugh scored 18 pts vs 24.5 line (-6.5), UNDER hit by 6.5 pts. Sensabaugh played 26 min (-5.2 vs L10 avg of 31.4) — 17% less than expected. Shooting efficiency was cold: 35.3% FG (-18.0% vs L10 avg of 53.3%). 6/17 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 22.5 pts — actual 18 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sensabaugh's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Filipowski scored 9 pts vs 19.5 line (-10.5), UNDER hit by 10.5 pts. Filipowski played 18 min (-9.0 vs L10 avg of 27.3) — 33% less than expected. Shooting efficiency was cold: 33.3% FG (-14.6% vs L10 avg of 47.9%). 3/9 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.5 pts — actual 9 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Filipowski's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Queen scored 17 pts vs 13.5 line (+3.5), UNDER missed by 3.5 pts. Queen played 37 min (+16.3 vs L10 avg of 20.9) — 78% more than expected. Shooting efficiency was hot: 66.7% FG (+27.1% vs L10 avg of 39.6%). 6/9 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.7 pts — actual 17 was 11.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="5" t="n">
         <v>21.5</v>
       </c>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>UTA @ NOP</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 20 pts vs 15.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 30 played vs L10 avg 31.1. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 47.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, Min Trend. Projection model targeted 19.1 pts — actual 20 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Achiuwa scored 13 pts vs 11.5 line (+1.5), UNDER missed by 1.5 pts. Achiuwa played 34 min (+4.6 vs L10 avg of 29.6) — 16% more than expected. Shooting efficiency was cold: 42.9% FG (-13.1% vs L10 avg of 56.0%). 6/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H. Projection model targeted 7.3 pts — actual 13 was 5.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clifford scored 12 pts vs 15.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 36 played vs L10 avg 33.5. Shooting efficiency was cold: 28.6% FG (-15.2% vs L10 avg of 43.8%). 4/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 13.3 pts — actual 12 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clifford in this role.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 1 pts vs 9.5 line (-8.5), OVER missed by 8.5 pts. Green played 27 min (-3.2 vs L10 avg of 30.3) — 11% less than expected. Shooting efficiency was cold: 0.0% FG (-44.2% vs L10 avg of 44.2%). 0/3 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Pace. Signals that were wrong: Trend, Context, Defense. Projection model targeted 12.4 pts — actual 1 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Stephen Curry</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Curry scored 17 pts vs 23.5 line (-6.5), UNDER hit by 6.5 pts. Curry played 25 min (-3.3 vs L10 avg of 28.3) — 12% less than expected. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 45.2%). Signals that called it correctly: H2H, FG Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.9 pts — actual 17 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Curry's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Melton scored 21 pts vs 13.5 line (+7.5), UNDER missed by 7.5 pts. Melton played 29 min (+4.1 vs L10 avg of 24.6) — 17% more than expected. Shooting efficiency was hot: 58.3% FG (+26.3% vs L10 avg of 32.0%). 7/12 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 13.7 pts — actual 21 was 7.3 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Raynaud scored 17 pts vs 16.5 line (+0.5), UNDER missed by 0.5 pts. Raynaud played 26 min (-6.8 vs L10 avg of 33.0) — 21% less than expected. Shooting efficiency was cold: 50.0% FG (-5.4% vs L10 avg of 55.4%). 7/14 from the field. Counter-signals that proved correct: HR L10, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 11.7 pts — actual 17 was 5.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Raynaud for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E77" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>WIN — II scored 12 pts vs 10.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 25 played vs L10 avg 24.2. Shooting was in line with averages: 71.4% FG (5/7, L10 avg 72.0%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Pace. Projection model targeted 14.1 pts — actual 12 was 2.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>SAC @ GSW</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Carter scored 6 pts vs 17.5 line (-11.5), UNDER hit by 11.5 pts. Carter played 21 min (-3.9 vs L10 avg of 24.5) — 16% less than expected. Shooting efficiency was hot: 60.0% FG (+18.0% vs L10 avg of 42.0%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 8.1 pts — actual 6 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Carter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Christie scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 29 played vs L10 avg 28.3. Shooting efficiency was cold: 12.5% FG (-28.3% vs L10 avg of 40.8%). 1/8 from the field. Counter-signals that proved correct: Volume, HR L30, Defense. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 7.3 pts — actual 12 was 4.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mathurin scored 9 pts vs 17.5 line (-8.5), OVER missed by 8.5 pts. Minutes were as expected: 27 played vs L10 avg 28.2. Shooting efficiency was cold: 12.5% FG (-34.0% vs L10 avg of 46.5%). 1/8 from the field. Counter-signals that proved correct: HR L30, Trend, H2H, Min Trend. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 18.1 pts — actual 9 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Collins scored 12 pts vs 11.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 28 played vs L10 avg 26.4. Shooting efficiency was cold: 45.5% FG (-5.2% vs L10 avg of 50.7%). 5/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 14.6 pts — actual 12 was 2.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 11 pts vs 8.5 line (+2.5), UNDER missed by 2.5 pts. Jr. played 24 min (-4.0 vs L10 avg of 27.5) — 15% less than expected. Shooting efficiency was cold: 40.0% FG (-5.2% vs L10 avg of 45.2%). 4/10 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 7.4 pts — actual 11 was 3.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Lopez scored 9 pts vs 10.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 25 played vs L10 avg 28.0. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 47.2%). Signals that called it correctly: HR L30, Context, H2H (3/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 7.0 pts — actual 9 was 2.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Lopez in this role.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dunn scored 2 pts vs 6.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 27 played vs L10 avg 25.7. Shooting efficiency was cold: 25.0% FG (-17.6% vs L10 avg of 42.6%). 1/4 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, H2H (7/10 aligned). Counter-signals that were wrong: Volume, Defense, Pace. Projection model targeted 5.4 pts — actual 2 was 3.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dunn's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Jordan Miller</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 4 pts vs 9.5 line (-5.5), UNDER hit by 5.5 pts. Miller played 16 min (-7.8 vs L10 avg of 24.0) — 32% less than expected. Shooting efficiency was hot: 100.0% FG (+46.3% vs L10 avg of 53.7%). 1/1 from the field. Signals that called it correctly: Trend, H2H, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.0 pts — actual 4 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Miller in this role.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Flagg scored 25 pts vs 27.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 34 played vs L10 avg 35.4. Shooting efficiency was cold: 36.0% FG (-11.0% vs L10 avg of 47.0%). 9/25 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 24.1 pts — actual 25 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Flagg in this role.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E87" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Leonard scored 34 pts vs 28.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 30 played vs L10 avg 30.1. Shooting was in line with averages: 57.9% FG (11/19, L10 avg 53.7%). Signals that called it correctly: Context, Defense, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 31.0 pts — actual 34 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Leonard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Marshall scored 6 pts vs 15.5 line (-9.5), OVER missed by 9.5 pts. Marshall played 20 min (-11.1 vs L10 avg of 31.0) — 36% less than expected. Shooting efficiency was cold: 30.0% FG (-16.1% vs L10 avg of 46.1%). 3/10 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.7 pts — actual 6 was 12.7 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Marshall for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E89" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Garland scored 22 pts vs 20.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 28 played vs L10 avg 30.0. Shooting was in line with averages: 50.0% FG (9/18, L10 avg 51.2%). Signals that called it correctly: Context, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.0 pts — actual 22 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Garland in this role.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>DAL @ LAC</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E90" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 11 pts vs 11.5 line (-0.5), OVER missed by 0.5 pts. Thompson played 26 min (+5.1 vs L10 avg of 21.2) — 24% more than expected. Shooting efficiency was cold: 23.5% FG (-19.5% vs L10 avg of 43.0%). 4/17 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Pace. Signals that were wrong: Volume, Context, Defense. Projection model targeted 12.3 pts — actual 11 was 1.3 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="5" t="n">
         <v>7.5</v>
       </c>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E92" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Hachimura scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 26 played vs L10 avg 23.0. Shooting efficiency was hot: 70.0% FG (+14.9% vs L10 avg of 55.1%). 7/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, FG Trend. Projection model targeted 6.5 pts — actual 15 was 8.5 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wallace scored 5 pts vs 7.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 23 played vs L10 avg 22.8. Shooting efficiency was cold: 25.0% FG (-25.0% vs L10 avg of 50.0%). 1/4 from the field. Counter-signals that proved correct: HR L10, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 9.3 pts — actual 5 was 4.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Holmgren scored 15 pts vs 15.5 line (-0.5), UNDER hit by 0.5 pts. Holmgren played 22 min (-5.2 vs L10 avg of 27.2) — 19% less than expected. Shooting efficiency was hot: 60.0% FG (+5.6% vs L10 avg of 54.4%). 6/10 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.3 pts — actual 15 was 2.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Holmgren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>WIN — LaRavia scored 2 pts vs 11.5 line (-9.5), UNDER hit by 9.5 pts. LaRavia played 20 min (-5.3 vs L10 avg of 25.2) — 21% less than expected. Shooting efficiency was cold: 14.3% FG (-37.3% vs L10 avg of 51.6%). 1/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 6.5 pts — actual 2 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Jaylin Williams</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 0 pts vs 5.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 14 played vs L10 avg 16.6. Shooting efficiency was cold: 0.0% FG (-44.4% vs L10 avg of 44.4%). 0/0 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.4 pts — actual 0 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Ayton scored 3 pts vs 11.5 line (-8.5), UNDER hit by 8.5 pts. Ayton played 23 min (-3.0 vs L10 avg of 25.8) — 12% less than expected. Shooting efficiency was cold: 25.0% FG (-47.3% vs L10 avg of 72.3%). 1/4 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 6.3 pts — actual 3 was 3.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ayton's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E98" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 21 played vs L10 avg 23.9. Shooting efficiency was cold: 33.3% FG (-14.0% vs L10 avg of 47.3%). 3/9 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, H2H (8/10 aligned). Counter-signals that were wrong: Volume, HR L30. Projection model targeted 9.6 pts — actual 9 was 0.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dort scored 8 pts vs 7.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 23 played vs L10 avg 21.9. Shooting efficiency was hot: 50.0% FG (+13.8% vs L10 avg of 36.2%). 3/6 from the field. Signals that called it correctly: Volume, Trend, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 10.0 pts — actual 8 was 2.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Dort in this role.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Jared McCain</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>WIN — McCain scored 15 pts vs 7.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 16 played vs L10 avg 17.2. Shooting efficiency was hot: 62.5% FG (+23.2% vs L10 avg of 39.3%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 7.8 pts — actual 15 was 7.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms McCain's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>28.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gilgeous-Alexander scored 25 pts vs 28.5 line (-3.5), OVER missed by 3.5 pts. Gilgeous-Alexander played 28 min (-4.0 vs L10 avg of 32.0) — 12% less than expected. Shooting efficiency was hot: 66.7% FG (+5.2% vs L10 avg of 61.5%). 10/15 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 29.2 pts — actual 25 was 4.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Hartenstein scored 0 pts vs 7.5 line (-7.5), UNDER hit by 7.5 pts. Hartenstein played 10 min (-10.8 vs L10 avg of 21.1) — 51% less than expected. Shooting efficiency was cold: 0.0% FG (-42.3% vs L10 avg of 42.3%). 0/1 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 6.3 pts — actual 0 was 6.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hartenstein's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Luke Kennard</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAL</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E103" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Kennard scored 10 pts vs 15.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 23 played vs L10 avg 24.4. Shooting efficiency was hot: 57.1% FG (+12.6% vs L10 avg of 44.5%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 7.9 pts — actual 10 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E104" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 15 pts vs 18.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 29.3. Shooting efficiency was cold: 35.7% FG (-9.2% vs L10 avg of 44.9%). 5/14 from the field. Signals that called it correctly: Volume, Context, Defense, Pace (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 17.5 pts — actual 15 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E105" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 22 pts vs 16.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 36 played vs L10 avg 38.1. Shooting efficiency was hot: 62.5% FG (+5.9% vs L10 avg of 56.6%). 10/16 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (7/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 21.7 pts — actual 22 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E106" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 12 pts vs 12.5 line (-0.5), OVER missed by 0.5 pts. Sheppard played 21 min (-8.2 vs L10 avg of 29.4) — 28% less than expected. Shooting efficiency was hot: 55.6% FG (+9.7% vs L10 avg of 45.9%). 5/9 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.5 pts — actual 12 was 1.5 pts close (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Sheppard for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E107" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brooks scored 10 pts vs 16.5 line (-6.5), OVER missed by 6.5 pts. Brooks played 33 min (+4.6 vs L10 avg of 28.3) — 16% more than expected. Shooting efficiency was cold: 25.0% FG (-12.4% vs L10 avg of 37.4%). 3/12 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 21.2 pts — actual 10 was 11.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E108" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 12 pts vs 18.5 line (-6.5), OVER missed by 6.5 pts. Sengun played 28 min (-5.3 vs L10 avg of 33.3) — 16% less than expected. Shooting efficiency was cold: 33.3% FG (-30.5% vs L10 avg of 63.8%). 5/15 from the field. Counter-signals that proved correct: HR L30, H2H, Pace. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 19.8 pts — actual 12 was 7.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Sengun for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E109" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 12 pts vs 8.5 line (+3.5), OVER hit by 3.5 pts. Eason played 31 min (+8.4 vs L10 avg of 22.7) — 37% more than expected. Shooting efficiency was hot: 71.4% FG (+37.1% vs L10 avg of 34.3%). 5/7 from the field. Signals that called it correctly: Volume, Trend, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Defense. Projection model targeted 13.3 pts — actual 12 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Eason in this role.</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E110" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 31 pts vs 24.5 line (+6.5), UNDER missed by 6.5 pts. Booker played 38 min (+5.5 vs L10 avg of 33.0) — 17% more than expected. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 45.4%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 22.7 pts — actual 31 was 8.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Booker's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E111" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 24 pts vs 24.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 36 played vs L10 avg 35.5. Shooting efficiency was cold: 40.0% FG (-14.5% vs L10 avg of 54.5%). 8/20 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 26.5 pts — actual 24 was 2.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Mark Williams</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E112" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 19 pts vs 9.5 line (+9.5), UNDER missed by 9.5 pts. Williams played 28 min (+7.4 vs L10 avg of 20.6) — 36% more than expected. Shooting efficiency was hot: 77.8% FG (+22.9% vs L10 avg of 54.9%). 7/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 5.9 pts — actual 19 was 13.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>Jordan Goodwin</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E113" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Goodwin scored 11 pts vs 7.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 25 played vs L10 avg 25.4. Shooting efficiency was hot: 57.1% FG (+15.4% vs L10 avg of 41.7%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Min Trend. Signals that were wrong: Trend, Context, Defense. Projection model targeted 7.2 pts — actual 11 was 3.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E114" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 20 pts vs 13.5 line (+6.5), OVER hit by 6.5 pts. Jr. played 39 min (+3.2 vs L10 avg of 35.5) — 9% more than expected. Shooting efficiency was cold: 33.3% FG (-10.1% vs L10 avg of 43.4%). 6/18 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 15.2 pts — actual 20 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gillespie scored 0 pts vs 8.5 line (-8.5), OVER missed by 8.5 pts. Gillespie played 17 min (-11.8 vs L10 avg of 28.8) — 41% less than expected. Shooting efficiency was cold: 0.0% FG (-36.5% vs L10 avg of 36.5%). 0/2 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.8 pts — actual 0 was 8.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Gillespie for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>HOU @ PHX</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="4" t="n">
         <v>6.5</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — O'Neale scored 3 pts vs 6.5 line (-3.5), OVER missed by 3.5 pts. O'Neale played 17 min (-7.7 vs L10 avg of 24.8) — 31% less than expected. Shooting efficiency was cold: 25.0% FG (-20.9% vs L10 avg of 45.9%). 1/4 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.2 pts — actual 3 was 4.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag O'Neale for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-08 10:04</t>
+        </is>
       </c>
     </row>
   </sheetData>
